--- a/excel/excel/Global.xlsx
+++ b/excel/excel/Global.xlsx
@@ -1020,8 +1020,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="5" outlineLevelCol="2"/>
+  <dimension ref="A1:C8"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20.1" customHeight="1" outlineLevelRow="7" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="6.25" customWidth="1"/>
     <col min="2" max="3" width="10.625" customWidth="1"/>
@@ -1086,6 +1086,22 @@
       </c>
       <c r="B6">
         <v>1001</v>
+      </c>
+    </row>
+    <row r="7" customHeight="1" spans="1:3">
+      <c r="A7">
+        <v>3</v>
+      </c>
+      <c r="B7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" customHeight="1" spans="1:3">
+      <c r="A8">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>30</v>
       </c>
     </row>
   </sheetData>

--- a/excel/excel/Global.xlsx
+++ b/excel/excel/Global.xlsx
@@ -4,13 +4,13 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11775"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="Global" sheetId="5" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Global!$A$4:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Global!$A$4:$B$8</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -56,7 +56,7 @@
     <t>c/s</t>
   </si>
   <si>
-    <t>{{reward_type = 3,item_type = 1001,item_count = 1},{reward_type = 4,item_type = 1,item_count = 1000}}</t>
+    <t>{{reward_type = 1,item_type = 1,item_count = 1000},{reward_type = 1,item_type = 2,item_count = 1000},{reward_type = 3,item_type = 1001,item_count = 1},{reward_type = 4,item_type = 1,item_count = 1000}}</t>
   </si>
 </sst>
 </file>
@@ -1105,7 +1105,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:B6" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A4:B8" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
